--- a/api/templates/device_summary_report/fr.xlsx
+++ b/api/templates/device_summary_report/fr.xlsx
@@ -1,46 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/device_summary_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B188112-8EA1-1E4C-9FDD-EF5C355BD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
   </bookViews>
   <sheets>
-    <sheet name="Device Summary Report" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Device Summary Report" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Rapport récapitulatif sur l’appareil</t>
+  </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">Notes
+Les catégories de résultats sont représentées par toutes les combinaisons de résultats possibles que GeneXpert envoie à Aspect. Par exemple, MTB Detected n’inclut pas les RIF détectés MTB Detected, car ils sont considérés comme des résultats différents</t>
+  </si>
+  <si>
     <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
   </si>
   <si>
@@ -53,12 +38,24 @@
     <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Appareil</t>
+  </si>
+  <si>
+    <t>Dernier téléchargement</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
+    <t>Autre</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
@@ -69,70 +66,61 @@
   </si>
   <si>
     <t>&lt;totalOtherTests&gt;</t>
-  </si>
-  <si>
-    <t>Rapport récapitulatif sur l’appareil</t>
-  </si>
-  <si>
-    <t>Notes
-Les catégories de résultats sont représentées par toutes les combinaisons de résultats possibles que GeneXpert envoie à Aspect. Par exemple, MTB Detected n’inclut pas les RIF détectés MTB Detected, car ils sont considérés comme des résultats différents</t>
-  </si>
-  <si>
-    <t>Appareil</t>
-  </si>
-  <si>
-    <t>Dernier téléchargement</t>
-  </si>
-  <si>
-    <t>Autre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -158,33 +146,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -193,28 +165,28 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -223,74 +195,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -618,116 +522,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.1640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.33203125" customWidth="1"/>
-    <col min="2" max="2" width="27" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="2" max="3" width="27" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.1640625" customWidth="1"/>
     <col min="5" max="5" width="27.6640625" customWidth="1"/>
     <col min="999" max="1008" width="9.33203125" customWidth="1"/>
     <col min="16369" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1024" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="34.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:1024" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:1024" ht="17" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:1024" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:1024" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" ht="57.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:1024" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+    <row r="9" ht="67.5" customHeight="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="ALU9"/>
-      <c r="ALV9"/>
-      <c r="ALW9"/>
-      <c r="ALX9"/>
-      <c r="ALY9"/>
-      <c r="ALZ9"/>
-      <c r="AMA9"/>
-      <c r="AMB9"/>
-      <c r="AMC9"/>
-      <c r="AMD9"/>
-      <c r="AME9"/>
-      <c r="AMF9"/>
-      <c r="AMG9"/>
-      <c r="AMH9"/>
-      <c r="AMI9"/>
-      <c r="AMJ9"/>
-    </row>
-    <row r="10" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>9</v>
-      </c>
       <c r="D10" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="13"/>
@@ -735,11 +625,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="E2:E7"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>

--- a/api/templates/device_summary_report/fr.xlsx
+++ b/api/templates/device_summary_report/fr.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -177,6 +177,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -577,7 +578,7 @@
       <c r="E6" s="4"/>
     </row>
     <row r="7" ht="57.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="4"/>
@@ -586,42 +587,42 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" ht="67.5" customHeight="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" ht="67.5" customHeight="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/api/templates/device_summary_report/fr.xlsx
+++ b/api/templates/device_summary_report/fr.xlsx
@@ -38,7 +38,7 @@
     <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -177,7 +177,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -578,7 +577,7 @@
       <c r="E6" s="4"/>
     </row>
     <row r="7" ht="57.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="4"/>
@@ -587,42 +586,42 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" ht="67.5" customHeight="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" ht="67.5" customHeight="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
